--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -991,7 +991,7 @@
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.26</v>
@@ -1014,7 +1014,7 @@
         <v>-0.22</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.43</v>
@@ -1037,7 +1037,7 @@
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.06</v>
@@ -1060,7 +1060,7 @@
         <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.14</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_antofagasta.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
